--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0086.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0086.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Mở khóa bằng cách sở hữu Resonator</t>
+          <t>Chiêu mộ Resonator để mở khóa</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Mở khóa bằng cách sở hữu Trang Phục Resonator</t>
+          <t>Lấy Trang Phục Resonator để mở khóa</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Sự kiện Hạn chế 2025: Quà Tặng Lễ Kỷ Niệm Hoành Tráng</t>
+          <t>Sự Kiện Hạn Chế Quà Tặng Đại Kỷ Niệm 2025</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hương Trà</t>
+          <t>Hương Trà Thơm Ngát</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Outstanding Commander</t>
+          <t>Chỉ huy xuất sắc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TD Terminator</t>
+          <t>Kẻ Tiêu Diệt Tacet</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Thăng Trầm</t>
+          <t>Thịnh Suy</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Post-Doomsday Coffee</t>
+          <t>Cà Phê Hậu Tận Thế</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Mellow Hours</t>
+          <t>Những Giờ Phút Thanh Bình</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Come On, Smile</t>
+          <t>Nào, cười lên đi</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Sự kiện</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Moonlit Path</t>
+          <t>Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Mời Tất Cả Bạn Đồng Hành</t>
+          <t>Mời Tất Cả Đồng Hành</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Cứu Con Mèo!</t>
+          <t>Cứu con mèo đi!</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Broken Dream</t>
+          <t>Giấc Mơ Tan Vỡ</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Resonators: Relink</t>
+          <t>Resonator: Kết Nối Lại</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hoàn Thành Nhiệm Vụ Chính: Khi Đêm Gõ Cửa</t>
+          <t>Hoàn thành Nhiệm vụ Chính: Khi Bóng Đêm Gõ Cửa.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Gia Nhập Hội Thẳm Sâu</t>
+          <t>Bước vào Hội Kín Vực Sâu</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Hoàn Thành Nhiệm Vụ Chính "Ngọn Gió Thánh Thường Xuyên Thổi"</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Làn Gió Thánh Thường Xuyên Thổi"</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Chứng Kiến Kết Thúc Lễ Hội Carnevale</t>
+          <t>Chứng kiến hồi kết của Carnevale.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Khám Phá Thành Phố Ragunna</t>
+          <t>Khám phá 40% Thành Phố Ragunna</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Điểm Kho Báu Một Lần</t>
+          <t>Hoàn thành thử thách Điểm Kho Báu một lần</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Đánh Bại Sentry Construct Trong Hầm Averardo</t>
+          <t>Đánh bại Sentry Construct trong Hầm Averardo</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Bảng Màu Tràn 3 Lần</t>
+          <t>Hoàn thành Thử Thách Bảng Màu Tràn đầy ba lần</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Khám Phá Hầm Averardo</t>
+          <t>Khám phá 40% Khu Lưu Trữ Averardo</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Musicfly Một Lần</t>
+          <t>Hoàn thành thử thách Musicfly một lần</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hoàn Thành Nhiệm Vụ Phụ "Hành Trình Niềm Tin"</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Hành Trình Niềm Tin"</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Dream Patrol 2 Lần</t>
+          <t>Hoàn thành thử thách Tuần Tra Giấc Mơ hai lần</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đến Fool's Elysium Và Luyện Khiêu Vũ Với Carlotta</t>
+          <t>Đến Fool's Elysium và tập nhảy với Carlotta</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Khám Phá Penitent's End</t>
+          <t>Khám phá 40% Kết Cục Sám Hối</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Hoàn Thành Tactical Hologram: Vitreum Dancer Một Lần</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Vitreum Dancer (Lần 1)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Ba Anh Em Nhà Fratelli 3 Lần</t>
+          <t>Hoàn thành thử thách Ba Anh Em Fratelli ba lần</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Dream Patrol Một Lần</t>
+          <t>Hoàn thành thử thách Tuần Tra Giấc Mơ một lần</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Khám Phá Hallowed Reach</t>
+          <t>Đạt 40% Tiến Độ Thám Hiểm tại Vùng Đất Thiêng</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Trải Nghiệm Wingray và Flight</t>
+          <t>Trải Nghiệm Wingray và Bay Lượn</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Phụ "The Last Knight"</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Hiệp Sĩ Cuối Cùng"</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Phụ "The Best Audience"</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Khán Giả Tốt Nhất"</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Thám Hiểm tại Whisperwind Haven</t>
+          <t>Đạt 40% Tiến Độ Thám Hiểm tại Thung Lũng Gió Thì Thầm</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Trải nghiệm Cruise Share một lần</t>
+          <t>Chia sẻ Chuyến Du Hành Kinh Nghiệm một lần</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Ba Anh Em Fratelli một lần</t>
+          <t>Hoàn thành thử thách Ba Anh Em Fratelli một lần</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Hymn of the Sea of Clouds: Storm"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Khúc Ca Biển Mây: Bão Tố"</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Thám Hiểm tại Nimbus Sanctum</t>
+          <t>Khám phá 40% Thánh Điện Nimbus</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Đánh bại Lifer</t>
+          <t>Hạ gục Lifer.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Where Wind Returns to Celestial Realms"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Nơi Gió Trở Về Cõi Thiêng"</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Vượt qua Wailing Ascent</t>
+          <t>Vượt qua Con Đường Than Khóc</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Thám Hiểm tại Fagaceae Peninsula</t>
+          <t>Khám phá 40% Bán Đảo Fagaceae</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Shadow of the Towers: Command Rise"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Bóng Tối Của Những Tòa Tháp: Sự Trỗi Dậy Của Chỉ Huy."</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Echo: Illusion một lần</t>
+          <t>Hoàn thành Thử thách Echo: Illusion một lần</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Phụ "Trials of Old"</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Thử Thách Cổ Xưa"</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến Độ Thám Hiểm tại Thessaleo Fells</t>
+          <t>Đạt 40% Tiến Độ Thám Hiểm tại Vùng Đất Thessaleo</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi phát hiện bất kỳ thử thách "Ruins Where Shadows Roam"</t>
+          <t>Mở khóa sau khi khám phá thử thách "Tàn Tích Bóng Tối Lang Thang" bất kỳ.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Hymn of the Sea of Clouds: Rainbow" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Khúc Ca Biển Mây: Cầu Vồng" để mở khóa</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kích hoạt các bia đá tại Shores of Last Breath để mở khóa</t>
+          <t>Nạp năng lượng cho các bia đá tại Bờ Vực Hơi Thở Cuối để mở khóa</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>January 31</t>
+          <t>Ngày 31 tháng 1</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Troupe of Fools</t>
+          <t>Đoàn Hội Ngớ Ngẩn</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Stage in the Box</t>
+          <t>Sân Khấu Trong Hộp.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>The Montelli Family</t>
+          <t>Gia Tộc Montelli</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Reshaping Dimensions</t>
+          <t>Tái cấu trúc không gian</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Shen Huasang</t>
+          <t>Thẩm Hoa Sướng</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Yan Yeqiao</t>
+          <t>Yan Dã Kiều</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Portable Confetti Pistol</t>
+          <t>Súng Giấy Pháo Di Động</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Pero's Peculiar Box</t>
+          <t>Chiếc Hộp Kỳ Lạ của Pero</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Luceanite Prop Set</t>
+          <t>Bộ đạo cụ Luceanite</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Art's Return</t>
+          <t>Sự Trở Lại Của Nghệ Thuật</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Executor's Case</t>
+          <t>Hồ Sơ Kẻ Thi Hành</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Family's Creed</t>
+          <t>Tín Điều Gia Tộc</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Golden Harpoon</t>
+          <t>Lao Vàng</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Safe Voyage</t>
+          <t>Hành Trình Bình An</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Old Ticket</t>
+          <t>Vé Cũ</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Peculiar Box</t>
+          <t>Chiếc Hộp Kỳ Lạ</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Sân Khấu Mới</t>
+          <t>Giai Đoạn Mới</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Cược và Nghệ Thuật</t>
+          <t>Nghệ Thuật Cọc</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Past Overdue</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Điệu Nhảy Tử Thần Trong Phòng Khiêu Vũ</t>
+          <t>Vũ Hội Tử Thần</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Nhân Danh Montellis</t>
+          <t>Nhân Danh Gia Tộc Montelli</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Vảy Vàng Ngoại Hoàng Long I</t>
+          <t>Vảy Rồng Huanglong Ngoại I</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Vảy Vàng Ngoại Hoàng Long II</t>
+          <t>Vảy Rồng Vàng Ngoài Huanglong II</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Báo Cáo Dự Án Xây Dựng Thành Phố Jinzhou I</t>
+          <t>Báo cáo Dự án Xây dựng Thành phố Jinzhou I</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Báo Cáo Dự Án Xây Dựng Thành Phố Jinzhou II</t>
+          <t>Báo cáo Dự án Xây dựng Thành phố Jinzhou II</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Lonely SOL-3: Central Plains I</t>
+          <t>SOL-3 Cô Đơn: Central Plains I</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Lonely SOL-3: Central Plains II</t>
+          <t>SOL-3 Cô Đơn: Central Plains II</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Đàn Chim Phi Thường I</t>
+          <t>Đàn Kỳ Dị I</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Đàn Chim Phi Thường II</t>
+          <t>Đàn Kỳ Dị II</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>An Unfaded Recording I</t>
+          <t>Bản Ghi Âm Không Phai Mờ I</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>An Unfaded Recording II</t>
+          <t>Bản Ghi Âm Không Phai Mờ II</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Báo Cáo Hành Vi Của Các Hoochief Tại Rừng Mờ I</t>
+          <t>Báo Cáo Hành Vi Của Các Thủ Lĩnh Hoochief Trong Rừng Âm U I</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Báo Cáo Hành Vi Của Các Hoochief Tại Rừng Mờ II</t>
+          <t>Báo Cáo Hành Vi về Bộ Lạc Hoochief tại Rừng Mờ II</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Criminal Sociology: The Exiles I</t>
+          <t>Xã Hội Học Tội Phạm: Những Kẻ Lưu Đày I</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Criminal Sociology: The Exiles II</t>
+          <t>Xã Hội Học Tội Phạm: Những Kẻ Lưu Đày II</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Nhật Ký Điều Tra Thung Lũng Norfall Của Đội Kỵ Binh Tuần Tra I</t>
+          <t>Nhật Ký Điều Tra Thung Lũng Norfall Của Đội Tuần Duyên I</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Nhật Ký Điều Tra Thung Lũng Norfall Của Đội Kỵ Binh Tuần Tra II</t>
+          <t>Nhật Ký Điều Tra Thung Lũng Norfall Của Đội Tuần Duyên II</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>"Đánh Giá Vở Kịch 'Chuyện Tình Hai Chim Non'" I</t>
+          <t>"Đánh giá "Chuyện Tình Hai Chim Đôi" I</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>"Đánh Giá Vở Kịch 'Chuyện Tình Hai Chim Non'" II</t>
+          <t>"Đánh giá "Chuyện Tình Hai Chim Đôi" II</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Giới Thiệu Cơ Bản Về Bờ Biển Đen I</t>
+          <t>Giới Thiệu Vùng Bờ Đen I</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Giới Thiệu Cơ Bản Về Bờ Biển Đen II</t>
+          <t>Giới Thiệu Vùng Bờ Đen II</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Báo Cáo Khảo Sát Mạch Lampylumen I</t>
+          <t>Báo cáo khảo sát về Mạch Lampylumen I</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Báo Cáo Khảo Sát Mạch Lampylumen II</t>
+          <t>Báo cáo khảo sát về Mạch Lampylumen II</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>SOL-3 Cô Đơn: Ấn Phẩm Đặc Biệt Suối Nước Nóng Hongzhen I</t>
+          <t>SOL-3 Cô Đơn: Hongzhen Hot Springs Special Edition I</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>SOL-3 Cô Đơn: Ấn Phẩm Đặc Biệt Suối Nước Nóng Hongzhen II</t>
+          <t>SOL-3 Cô Đơn: Hongzhen Hot Springs Special Edition II</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Giới thiệu Nâng cao về Bờ Đen I</t>
+          <t>Giới Thiệu Sơ Bộ Bờ Biển Đen I (Cao Cấp)</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Giới thiệu Nâng cao về Bờ Đen II</t>
+          <t>Giới Thiệu Sơ Bộ Bờ Biển Đen II (Cao Cấp)</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Bộ Luật Vực Sâu: Triết Lý Trật Tự I</t>
+          <t>Bộ Luật Thâm Uyên: Triết Lý Trật Tự I</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Bộ Luật Vực Sâu: Triết Lý Trật Tự II</t>
+          <t>Bộ Luật Thâm Uyên: Triết Lý Trật Tự II</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Những Quý Ông Trước Cửa I</t>
+          <t>Những Quý Ông Tại Cửa I</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Những Quý Ông Trước Cửa II</t>
+          <t>Những Quý Ông Tại Cửa II</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Ragunna: A Minority Report I</t>
+          <t>Ragunna: Bản Báo Cáo Thiểu Số I</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Ragunna: A Minority Report II</t>
+          <t>Ragunna: Bản Báo Cáo Thiểu Số II</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Echoes from Ragunna's Past I</t>
+          <t>Echo từ Quá khứ Ragunna I</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Echoes from Ragunna's Past II</t>
+          <t>Echo từ Quá khứ Ragunna II</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Within Nimbus Sanctum I</t>
+          <t>Bên trong Nimbus Sanctum I</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Within Nimbus Sanctum II</t>
+          <t>Bên trong Nimbus Sanctum II</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Nguyện Ước Hộ Vệ Ban Phước Lành Cho Rinascita I</t>
+          <t>Nguyện Sentinel phù hộ cho Rinascita I</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Nguyện Ước Hộ Vệ Ban Phước Lành Cho Rinascita II</t>
+          <t>Nguyện Sentinel phù hộ cho Rinascita II</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Defendant's Witness I</t>
+          <t>Nhân Chứng I của Bị Cáo</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Defendant's Witness II</t>
+          <t>Nhân Chứng II của Bị Cáo</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Averardo Vault Employee Manual I</t>
+          <t>Sổ Tay Nhân Viên Kho Tàng Averardo I</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Averardo Vault Employee Manual II</t>
+          <t>Sổ tay Nhân viên Hầm Averardo II</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Riccioli Islands Promotional Poster I</t>
+          <t>Áp Phích Quảng Cáo Quần Đảo Riccioli I</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Riccioli Islands Promotional Poster II</t>
+          <t>Áp Phích Quảng Cáo Quần Đảo Riccioli II</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Dream Patrol</t>
+          <t>Tuần Tra Giấc Mơ</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Vitreum Dancer</t>
+          <t>Hologram Chiến Thuật: Vũ Công Vitreum</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Dream Patrol: Nightmare</t>
+          <t>Tuần Tra Giấc Mộng: Ác Mộng</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Ruins Where Shadows Roam</t>
+          <t>Tàn Tích Nơi Bóng Tối Lang Thang</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Thử Thách Echo: Ảo Ảnh</t>
+          <t>Thử Thách Tiếng Vọng: Ảo Ảnh</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Sonance Casket: Ragunna</t>
+          <t>Hòm Thanh Âm: Ragunna</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Bờ Hơi Thở Cuối Cùng</t>
+          <t>Bờ Biển Hơi Thở Cuối Cùng</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Oakheart Highcourt</t>
+          <t>Tòa Thượng Nghị Oakheart</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Thử Thách Echo: Hacker Vũ Điệu</t>
+          <t>Thử Thách Tiếng Vọng: Vũ Điệu Hacker</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Chuyển Bản Đồ</t>
+          <t>Chuyển bản đồ</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>White: The Hollow Space</t>
+          <t>Trắng: Không Gian Rỗng</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Blue: The Indifferent Soul</t>
+          <t>Xanh: Linh Hồn Lãnh Đạm</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Đen: Chặng Đường Kết Thúc</t>
+          <t>Đen: Chặng Đường Cuối Cùng</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Orange: The Furious Roar</t>
+          <t>Orange: Tiếng Gầm Phẫn Nộ</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Yellow: The Warning Sign</t>
+          <t>Màu Vàng: Dấu Hiệu Cảnh Báo</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Green: The False Appearance</t>
+          <t>Màu Xanh: Diện Mạo Giả Tạo</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Red: The Destructive Force</t>
+          <t>Màu Đỏ: Lực Lượng Hủy Diệt</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Grey: The Insincere Face</t>
+          <t>Grey: Gương Mặt Giả Dối</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Purple: The Mysterious Flame</t>
+          <t>Tím: Ngọn Lửa Bí Ẩn</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: Chaotic Juncture</t>
+          <t>Thử Thách Hàng Tuần: Giao Lộ Hỗn Mang</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: The Fated Confrontation</t>
+          <t>Thử Thách Hàng Tuần: Đối Đầu Định Mệnh</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: Beyond the Crimson Curtain</t>
+          <t>Thử thách Hàng tuần: Vượt Qua Bức Màn Đỏ</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: The Wheel of Broken Fate</t>
+          <t>Thử Thách Hàng Tuần: Bánh Xe Định Mệnh Vỡ Tan</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: Bell of Archaic Chants</t>
+          <t>Thử thách Hàng tuần: Chuông Thánh Ca Cổ Xưa</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Sử dụng Electro Flare để có lợi thế chiến đấu</t>
+          <t>Tận dụng Tia sáng Electro để chiếm ưu thế trong chiến đấu</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Không thể mở bánh xe Tiện Ích ở trạng thái hiện tại</t>
+          <t>Hiện không thể mở bánh xe Tiện Ích</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Chưa lấp đầy không gian Bán Nhanh</t>
+          <t>Vị trí Bán Nhanh chưa được lấp đầy</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Đã chọn các vật phẩm không thể bán</t>
+          <t>Đã chọn vật phẩm không thể bán</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Tất cả vật phẩm có thể bán đã được bán</t>
+          <t>Tất cả vật phẩm có thể bán đã được bán hết</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Tổng điểm</t>
+          <t>Tổng Điểm</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Vui lòng xử lý vật phẩm đã chọn trước</t>
+          <t>Trước tiên, hãy xử lý món đồ đã chọn đi.</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Player Info</t>
+          <t>Thông Tin Người Chơi</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Nhấn nút khi súng giáo nằm trong vùng sáng để tăng tiến độ</t>
+          <t>Nhấn nút khi súng lao nằm trong vùng sáng để tăng tiến độ.</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Unlocked Echoes</t>
+          <t>Mở khóa Echo</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Tất cả Ngày</t>
+          <t>Cả Ngày</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Daytime</t>
+          <t>Ban Ngày</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Đêm</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Hàng hóa</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Khả năng câu cá</t>
+          <t>Kỹ Năng Câu Cá</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Available Time</t>
+          <t>Thời gian mở</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Kho Dự Trữ</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Lượt Thu Hoạch Tiếp Theo</t>
+          <t>Thu hoạch tiếp theo</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Save As Preset</t>
+          <t>Lưu Làm Cài Đặt Mẫu</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Glamour Couture</t>
+          <t>Thời Trang Lộng Lẫy</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Chiến Binh Mưu Kế Kẹp Đòn</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Thử Thách trong Glamour Couture</t>
+          <t>Hoàn thành Thử Thách Thời Trang Lộng Lẫy trong Glamour Couture</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Đạt 3.000 điểm trong Calamity Arena của Pincer Maneuver Warriors III</t>
+          <t>Đạt 3.000 điểm trong Calamity Arena của Pincer Maneuver Warriors III.</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Đạt 6.000 điểm trong Endless Arena của Pincer Maneuver Warriors III</t>
+          <t>Thu thập 6.000 điểm trong Đấu Trường Bất Tận Chiến Binh Kẹp Đòn III</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Đạt 3.000 điểm trong Calamity Arena của Pincer Maneuver Warriors IV</t>
+          <t>Đạt 3.000 điểm trong Calamity Arena của Pincer Maneuver Warriors IV.</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Đạt 6.000 điểm trong Endless Arena của Pincer Maneuver Warriors IV</t>
+          <t>Đạt 6.000 điểm trong Đấu Trường Vô Tận của Chiến Binh Kẹp Chuyển IV</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm trong Starry Night Over Ragunna của Although Colors Have Không Form</t>
+          <t>Đạt 2.000 điểm trong Starry Night Over Ragunna of Although Colors Have No Form</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Đạt 4.400 điểm trong Pilgrim in the Sea of Fog của Although Colors Have Không Form</t>
+          <t>Đạt 4.400 điểm trong "Lữ Khách Trong Biển Sương Mù" thuộc sự kiện "Dù Màu Sắc Vô Hình".</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Đạt 4.400 điểm trong Faith Leading the People của Although Colors Have Không Form</t>
+          <t>Đạt 4.400 điểm trong "Đức Tin Dẫn Lối Nhân Dân" thuộc sự kiện "Dù Màu Sắc Vô Hình".</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Dùng Carlotta để vượt qua Tầng 1 &amp; Tầng 2 Hazard Tower trong Tower of Adversity: Hazard Zone</t>
+          <t>Dùng Carlotta để vượt qua Tầng 1 &amp; Tầng 2 của Tháp Hazard trong "Tháp Nghịch Cảnh: Vùng Nguy Hiểm"</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Dùng Roccia để vượt Tháp Nguy Hiểm Tầng 1 &amp; Tầng 2 trong Khu Vực Nguy Hiểm: Tháp Đối Kháng</t>
+          <t>Dùng Roccia để vượt qua Tầng 1 &amp; Tầng 2 Tháp Nguy Hiểm trong Tháp Thử Thách: Khu Vực Nguy Hiểm</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Catch List</t>
+          <t>Danh Sách Bắt</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Kích cỡ</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Wonder Bubble</t>
+          <t>Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Catches</t>
+          <t>Bắt lấy</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Trawl</t>
+          <t>Kéo lưới</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Preset Name</t>
+          <t>Tên Cài Đặt</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Không thể mời trong thiết lập đội</t>
+          <t>Trong thiết lập đội hình, không thể mời</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Echo Preset</t>
+          <t>Bản mẫu Echo</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Thiết lập hiện tại</t>
+          <t>Thiết Lập Hiện Tại</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Preset Applied</t>
+          <t>Đã Áp Dụng Cài Đặt Sẵn</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Preset Applied</t>
+          <t>Đã Áp Dụng Cài Đặt Sẵn</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Chỉ Số</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Tối đa 20 ký tự</t>
+          <t>Tối đa 20 nhân vật</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Add Filter</t>
+          <t>Thêm Bộ Lọc</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Vivid</t>
+          <t>Sống Động</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Dystopian</t>
+          <t>Hủy Diệt</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Film</t>
+          <t>Phim</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Wild</t>
+          <t>Hoang dã</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Có Sẵn</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Deliverable</t>
+          <t>Có thể giao</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Chấp Nhận</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Deliver</t>
+          <t>Giao hàng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Abandon</t>
+          <t>Bỏ mặc</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Không thể giao hàng</t>
+          <t>Không thể giao hàng.</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Câu Cá</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Câu Cá</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Vận chuyển</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Kiểm Tra Năng Lực Yêu Cầu</t>
+          <t>Kiểm tra Năng Lực Cần Thiết</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Adventure Log</t>
+          <t>Nhật ký phiêu lưu</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Catch Log</t>
+          <t>Nhật Ký Bắt</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ability Log</t>
+          <t>Nhật Ký Kỹ Năng</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Request Log</t>
+          <t>Nhật Ký Yêu Cầu</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Hủy Theo Dõi</t>
+          <t>Hủy theo dõi</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Coconut Urchin</t>
+          <t>Nhím Dừa</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Riccioli Black Pearl</t>
+          <t>Ngọc Trai Đen Riccioli</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Bampuff</t>
+          <t>Bom Bông</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Coast Flax</t>
+          <t>Cây Gai Bờ Biển</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Palm Tree Log</t>
+          <t>Khúc Gỗ Cây Cau</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Metal Debris</t>
+          <t>Mảnh Kim Loại Vụn</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Octopus Clam</t>
+          <t>Ngao Bạch Tuộc</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Bell-less Crab</t>
+          <t>Cua Không Chuông</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Airsailer</t>
+          <t>Thuyền Buồm Gió</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Fried Egg Jellyfish</t>
+          <t>Sứa Trứng Chiên</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Til the Fin-ish</t>
+          <t>Đến Khi Cá Chết</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Leafy Seadragon</t>
+          <t>Rồng Biển Lá</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Yarn Eel</t>
+          <t>Lươn Sợi</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Dumbo Octopus</t>
+          <t>Bạch Tuộc Dumbo</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Giant Gulper</t>
+          <t>Gulper Khổng Lồ</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Sob Blob</t>
+          <t>Quả cầu nước mắt</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Gooberstar</t>
+          <t>Ngôi sao ngốc nghếch</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Pricklecrab</t>
+          <t>Cua Gai</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Feather Star</t>
+          <t>Ngôi Sao Lông Vũ</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Stygian Phantom</t>
+          <t>Bóng Ma Stygian</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dead Man's Eye</t>
+          <t>Con Mắt Người Chết</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Seabed Snow</t>
+          <t>Tuyết Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Trapper Anglerfish</t>
+          <t>Cá Anglerfish thợ săn</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Titanium Mackerel</t>
+          <t>Cá Thu Titan</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Bubble Snail</t>
+          <t>Ốc Sên Bong Bóng</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Sunfish</t>
+          <t>Cá Mặt Trời</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Legilimens Shrimp</t>
+          <t>Tôm Thần Thám</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Lancetfish</t>
+          <t>Cá Kiếm</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Astrite Crab</t>
+          <t>Cua Astrite</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Tripod Fish</t>
+          <t>Cá Ba Chân</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Rainbow Dolphinfish</t>
+          <t>Cá Chuồn Cầu Vồng</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Trombone Ammonoid</t>
+          <t>Bạch Tuộc Kèn Trombone</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Reinfish</t>
+          <t>Cá Tăng Cường</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Aureo Shark</t>
+          <t>Cá mập Aureo</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Pink Hallowfin</t>
+          <t>Cá Hollowfin Hồng</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Pelagic Wyrm</t>
+          <t>Giun Biển Pelagic</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Overlord Squid</t>
+          <t>Mực Chúa Tể</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Bogie Shrimp</t>
+          <t>Tôm Quỷ</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Mutant: Coconut Urchin</t>
+          <t>Đột Biến: Nhím Dừa</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Mutant: Octopus Clam</t>
+          <t>Quái Mutant: Sò Bạch Tuộc</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Mutant: Bell-less Crab</t>
+          <t>Đột Biến: Cua Không Kêu</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Mutant: Airsailer</t>
+          <t>Đột Biến: Airsailer</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Mutant: Fried Egg Jellyfish</t>
+          <t>Quái Mutant: Sứa Trứng Rán</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Mutant: Til the Fin-ish</t>
+          <t>Quái đột biến: Til the Fin-ish</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Mutant: Leafy Seadragon</t>
+          <t>Quái Mutant: Cá Rồng Gai Lá</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Mutant: Yarn Eel</t>
+          <t>Quái đột biến: Lươn Sợi</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Mutant: Dumbo Octopus</t>
+          <t>Đột Biến: Bạch Tuộc Dumbo</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Mutant: Giant Gulper</t>
+          <t>Quái Mutant: Cá Mút Khổng Lồ</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mutant: Salp</t>
+          <t>Quái đột biến: Salp</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mutant: Sob Blob</t>
+          <t>Quái đột biến: Sob Blob</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Mutant: Pokey Moray</t>
+          <t>Quái Mutant: Lươn Gai Nhọn</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Mutant: Gooberstar</t>
+          <t>Quái Mutant: Sao Goober</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Mutant: Pricklecrab</t>
+          <t>Quái Mutant: Cua Gai</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Mutant: Clione</t>
+          <t>Đột Biến: Clione</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Mutant: Feather Star</t>
+          <t>Quái Mutant: Sao Lông Vũ</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Mutant: Stygian Phantom</t>
+          <t>Quái đột biến: Bóng Ma Stygian</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Mutant: Dead Man's Eye</t>
+          <t>Đột Biến: Mắt Người Chết</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Mutant: Seabed Snow</t>
+          <t>Quái đột biến: Tuyết Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Mutant: Trapper Anglerfish</t>
+          <t>Quái đột biến: Cá Mồm Câu Trapper</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Mutant: Titanium Mackerel</t>
+          <t>Quái đột biến: Cá Thu Titanium</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Mutant: Bubble Snail</t>
+          <t>Đột Biến: Ốc Bong Bóng</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Mutant: Sunfish</t>
+          <t>Quái đột biến: Cá Mặt Trời</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Mutant: Legilimens Shrimp</t>
+          <t>Quái Mutant: Tôm Thấu Thị</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Mutant: Lancetfish</t>
+          <t>Quái Mutant: Cá Đinh Ba</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Mutant: Astrite Crab</t>
+          <t>Đột Biến: Astrite Crab</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Mutant: Tripod Fish</t>
+          <t>Quái đột biến: Cá Ba Chân</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Mutant: Rainbow Dolphinfish</t>
+          <t>Quái Mutant: Cá Chuồn Cầu Vồng</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Mutant: Trombone Ammonoid</t>
+          <t>Quái đột biến: Ốc Trombone</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Mutant: Reinfish</t>
+          <t>Quái Mutant: Cá Cốt Thép</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Fame</t>
+          <t>Danh vọng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Basic Hull</t>
+          <t>Vỏ Cơ Bản</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Advanced Hull</t>
+          <t>Vỏ Tàu Cao Cấp</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Reaction Thruster</t>
+          <t>Động Cơ Phản Ứng</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Hydraulic Capstan</t>
+          <t>Tời Kéo Thủy Lực</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Capacity Nâng cấp I</t>
+          <t>Nâng cấp Dung lượng I</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Wonder Bubble</t>
+          <t>Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Gondola Spur Training</t>
+          <t>Huấn luyện Gondola Spur</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Abyssal Hull</t>
+          <t>Thân Tàu Vực Sâu</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Gondola Strength Training I</t>
+          <t>Huấn luyện sức mạnh Gondola I</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Four-Wheel Capstan</t>
+          <t>Tời Bốn Bánh</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Capacity Nâng cấp II</t>
+          <t>Nâng cấp Dung lượng II</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Trawl</t>
+          <t>Kéo lưới</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Nautical Light</t>
+          <t>Ánh Sáng Hàng Hải</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Oceanic Hull</t>
+          <t>Thân Tàu Hải Dương</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Gondola Stamina Training II</t>
+          <t>Huấn luyện sức bền Gondola II</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Rigid Fishing Device</t>
+          <t>Thiết Bị Câu Cá Cứng Nhắc</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Capacity Nâng cấp III</t>
+          <t>Nâng cấp Dung lượng III</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>"Sweet Puff" Tube</t>
+          <t>"Ống \"Bánh Ngọt Puff\""</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Bait</t>
+          <t>Mồi nhử</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Bổ Sung Engine Room</t>
+          <t>Phòng Máy Phụ</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Riccioli Islands Biology</t>
+          <t>Sinh Vật Học Quần Đảo Riccioli</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Danh Tiếng Vượt Biển</t>
+          <t>Danh Vọng Vượt Biển</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Voyage Litany</t>
+          <t>Kinh Hành Trình</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Recycle Techniques</t>
+          <t>Kỹ Thuật Tái Chế</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Forbidden Scrolls</t>
+          <t>Cuộn Sách Cấm</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Shallow</t>
+          <t>Nông cạn</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Deep</t>
+          <t>Sâu Thẳm</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Abyssal</t>
+          <t>Vực Sâu</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Oceanic</t>
+          <t>Hải Dương</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Wonder Bubble</t>
+          <t>Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Fishing Area</t>
+          <t>Khu Vực Câu Cá</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Available Time</t>
+          <t>Thời gian mở</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Smallest Catch</t>
+          <t>Mẻ Cá Nhỏ Nhất</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Biggest Catch</t>
+          <t>Mẻ Cá Lớn Nhất</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>First Entry Fame</t>
+          <t>Điểm Danh Lần Đầu</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Chưa ghi nhận</t>
+          <t>Chưa ghi lại</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
